--- a/apps/web/public/descargas/plantilla-bia.xlsx
+++ b/apps/web/public/descargas/plantilla-bia.xlsx
@@ -1,59 +1,248 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="BIA" sheetId="1" r:id="rId1"/>
-    <sheet name="Guía" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="BIA" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Guía" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+  <si>
+    <t>BIA — Análisis de Impacto al Negocio (ISO 22301)</t>
+  </si>
+  <si>
+    <t>Empresa:</t>
+  </si>
+  <si>
+    <t>Fecha:</t>
+  </si>
+  <si>
+    <t>Responsable:</t>
+  </si>
+  <si>
+    <t>Período analizado:</t>
+  </si>
+  <si>
+    <t>N°</t>
+  </si>
+  <si>
+    <t>Proceso</t>
+  </si>
+  <si>
+    <t>Responsable del proceso</t>
+  </si>
+  <si>
+    <t>Producto / Servicio afectado</t>
+  </si>
+  <si>
+    <t>Impacto financiero (1-5)</t>
+  </si>
+  <si>
+    <t>Impacto operativo (1-5)</t>
+  </si>
+  <si>
+    <t>Impacto legal (1-5)</t>
+  </si>
+  <si>
+    <t>Impacto reputacional (1-5)</t>
+  </si>
+  <si>
+    <t>Puntaje total</t>
+  </si>
+  <si>
+    <t>Criticidad</t>
+  </si>
+  <si>
+    <t>RTO — tiempo máx. recuperación</t>
+  </si>
+  <si>
+    <t>RPO — pérdida de datos tolerable</t>
+  </si>
+  <si>
+    <t>MTPD — interrupción máx. tolerable</t>
+  </si>
+  <si>
+    <t>Dependencias críticas</t>
+  </si>
+  <si>
+    <t>Facturación y cobranza</t>
+  </si>
+  <si>
+    <t>Resp. Administración</t>
+  </si>
+  <si>
+    <t>Facturación a clientes</t>
+  </si>
+  <si>
+    <t>ALTO</t>
+  </si>
+  <si>
+    <t>8 hs</t>
+  </si>
+  <si>
+    <t>4 hs</t>
+  </si>
+  <si>
+    <t>24 hs</t>
+  </si>
+  <si>
+    <t>Sistema ERP, conectividad a internet</t>
+  </si>
+  <si>
+    <t>Despacho de mercadería</t>
+  </si>
+  <si>
+    <t>Resp. Logística</t>
+  </si>
+  <si>
+    <t>Entregas a clientes</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>48 hs</t>
+  </si>
+  <si>
+    <t>Depósito, flota propia, WMS</t>
+  </si>
+  <si>
+    <t>Atención al cliente</t>
+  </si>
+  <si>
+    <t>Resp. Comercial</t>
+  </si>
+  <si>
+    <t>Soporte post-venta</t>
+  </si>
+  <si>
+    <t>72 hs</t>
+  </si>
+  <si>
+    <t>CRM, telefonía</t>
+  </si>
+  <si>
+    <t>Escalas: impacto 1 = despreciable … 5 = severo · RTO = tiempo máx. para restablecer · RPO = pérdida de datos tolerable · MTPD = interrupción máx. antes de daño inaceptable</t>
+  </si>
+  <si>
+    <t>Las filas 5-7 son ejemplos — borralas y cargá tu análisis. Puntaje y criticidad se calculan automáticamente.</t>
+  </si>
+  <si>
+    <t>CÓMO HACER EL BIA</t>
+  </si>
+  <si>
+    <t>1. Listá los procesos del negocio (tomalos del mapa de procesos si lo tenés).</t>
+  </si>
+  <si>
+    <t>2. Con el responsable de cada proceso, evaluá el impacto de una interrupción en 4 dimensiones (1-5).</t>
+  </si>
+  <si>
+    <t>3. El puntaje total y la criticidad se calculan automáticamente.</t>
+  </si>
+  <si>
+    <t>4. Definí RTO (cuánto tarda en volver a funcionar), RPO (cuántos datos podés perder) y MTPD (límite tolerable).</t>
+  </si>
+  <si>
+    <t>5. Anotá las dependencias: sistemas, personas clave, proveedores, infraestructura.</t>
+  </si>
+  <si>
+    <t>6. Los procesos CRÍTICOS son la prioridad del plan de continuidad del negocio.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TIP: en SGI360 el BIA alimenta los planes de continuidad y el mapa de procesos — cuando cambia un proceso, el análisis se actualiza solo → logismart.ar</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF94A3B8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF166534"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E40AF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE047"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF166534"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -61,18 +250,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF166534"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,270 +657,612 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>BIA — Análisis de Impacto al Negocio (ISO 22301)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Empresa:</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>Fecha:</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>Responsable:</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>N°</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Proceso</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Responsable del proceso</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Producto/Servicio afectado</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Impacto financiero (1-5)</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Impacto operativo (1-5)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Impacto legal/regulatorio (1-5)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Impacto reputacional (1-5)</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Puntaje total</v>
-      </c>
-      <c r="J4" t="str">
-        <v>RTO (máx. tiempo de recuperación)</v>
-      </c>
-      <c r="K4" t="str">
-        <v>RPO (máx. pérdida de datos)</v>
-      </c>
-      <c r="L4" t="str">
-        <v>MTPD (máx. interrupción tolerable)</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Dependencias críticas</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Criticidad</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
+    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="str">
-        <v>Ej: Facturación y cobranza</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Resp. Administración</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Facturación a clientes</v>
-      </c>
-      <c r="E5">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="34" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="6">
         <v>4</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="6">
         <v>3</v>
       </c>
-      <c r="I5" t="str">
-        <v>=SUM(E5:H5)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>8 hs</v>
-      </c>
-      <c r="K5" t="str">
-        <v>4 hs</v>
-      </c>
-      <c r="L5" t="str">
-        <v>24 hs</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Sistema ERP, internet</v>
-      </c>
-      <c r="N5" t="str">
-        <v>=IF(I5&gt;=16,"Crítico",IF(I5&gt;=10,"Alto","Medio"))</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
+      <c r="I5" s="7">
+        <f>SUM(E5:H5)</f>
+        <v>14</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" t="str">
-        <v>Ej: Despacho de mercadería</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Resp. Logística</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Entregas a clientes</v>
-      </c>
-      <c r="E6">
+      <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="9">
         <v>4</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="9">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="9">
         <v>2</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="9">
         <v>4</v>
       </c>
-      <c r="I6" t="str">
-        <v>=SUM(E6:H6)</v>
-      </c>
-      <c r="J6" t="str">
-        <v>4 hs</v>
-      </c>
-      <c r="K6" t="str">
-        <v>—</v>
-      </c>
-      <c r="L6" t="str">
-        <v>48 hs</v>
-      </c>
-      <c r="M6" t="str">
-        <v>Depósito, flota, WMS</v>
-      </c>
-      <c r="N6" t="str">
-        <v>=IF(I6&gt;=16,"Crítico",IF(I6&gt;=10,"Alto","Medio"))</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
+      <c r="I6" s="10">
+        <f>SUM(E6:H6)</f>
+        <v>15</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" t="str">
-        <v>Ej: Atención al cliente</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Resp. Comercial</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Soporte post-venta</v>
-      </c>
-      <c r="E7">
+      <c r="B7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="6">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="6">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="6">
         <v>2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="6">
         <v>4</v>
       </c>
-      <c r="I7" t="str">
-        <v>=SUM(E7:H7)</v>
-      </c>
-      <c r="J7" t="str">
-        <v>24 hs</v>
-      </c>
-      <c r="K7" t="str">
-        <v>—</v>
-      </c>
-      <c r="L7" t="str">
-        <v>72 hs</v>
-      </c>
-      <c r="M7" t="str">
-        <v>CRM, telefonía</v>
-      </c>
-      <c r="N7" t="str">
-        <v>=IF(I7&gt;=16,"Crítico",IF(I7&gt;=10,"Alto","Medio"))</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Escalas: impacto 1=despreciable … 5=severo · RTO=tiempo máx. para restablecer · RPO=pérdida de datos tolerable · MTPD=interrupción máx. antes de daño inaceptable</v>
-      </c>
+      <c r="I7" s="7">
+        <f>SUM(E7:H7)</f>
+        <v>11</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6">
+        <f>IF(COUNT(E8:H8)&gt;0,SUM(E8:H8),"")</f>
+      </c>
+      <c r="J8" s="6">
+        <f>IF(I8="","",IF(I8&gt;=16,"CRÍTICO",IF(I8&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6">
+        <f>IF(COUNT(E9:H9)&gt;0,SUM(E9:H9),"")</f>
+      </c>
+      <c r="J9" s="6">
+        <f>IF(I9="","",IF(I9&gt;=16,"CRÍTICO",IF(I9&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6">
+        <f>IF(COUNT(E10:H10)&gt;0,SUM(E10:H10),"")</f>
+      </c>
+      <c r="J10" s="6">
+        <f>IF(I10="","",IF(I10&gt;=16,"CRÍTICO",IF(I10&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6">
+        <f>IF(COUNT(E11:H11)&gt;0,SUM(E11:H11),"")</f>
+      </c>
+      <c r="J11" s="6">
+        <f>IF(I11="","",IF(I11&gt;=16,"CRÍTICO",IF(I11&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6">
+        <f>IF(COUNT(E12:H12)&gt;0,SUM(E12:H12),"")</f>
+      </c>
+      <c r="J12" s="6">
+        <f>IF(I12="","",IF(I12&gt;=16,"CRÍTICO",IF(I12&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6">
+        <f>IF(COUNT(E13:H13)&gt;0,SUM(E13:H13),"")</f>
+      </c>
+      <c r="J13" s="6">
+        <f>IF(I13="","",IF(I13&gt;=16,"CRÍTICO",IF(I13&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6">
+        <f>IF(COUNT(E14:H14)&gt;0,SUM(E14:H14),"")</f>
+      </c>
+      <c r="J14" s="6">
+        <f>IF(I14="","",IF(I14&gt;=16,"CRÍTICO",IF(I14&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6">
+        <f>IF(COUNT(E15:H15)&gt;0,SUM(E15:H15),"")</f>
+      </c>
+      <c r="J15" s="6">
+        <f>IF(I15="","",IF(I15&gt;=16,"CRÍTICO",IF(I15&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6">
+        <f>IF(COUNT(E16:H16)&gt;0,SUM(E16:H16),"")</f>
+      </c>
+      <c r="J16" s="6">
+        <f>IF(I16="","",IF(I16&gt;=16,"CRÍTICO",IF(I16&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6">
+        <f>IF(COUNT(E17:H17)&gt;0,SUM(E17:H17),"")</f>
+      </c>
+      <c r="J17" s="6">
+        <f>IF(I17="","",IF(I17&gt;=16,"CRÍTICO",IF(I17&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6">
+        <f>IF(COUNT(E18:H18)&gt;0,SUM(E18:H18),"")</f>
+      </c>
+      <c r="J18" s="6">
+        <f>IF(I18="","",IF(I18&gt;=16,"CRÍTICO",IF(I18&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6">
+        <f>IF(COUNT(E19:H19)&gt;0,SUM(E19:H19),"")</f>
+      </c>
+      <c r="J19" s="6">
+        <f>IF(I19="","",IF(I19&gt;=16,"CRÍTICO",IF(I19&gt;=10,"ALTO","MEDIO")))</f>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="21" ht="26" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
-  </ignoredErrors>
+  <mergeCells count="3">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A22:N22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>CÓMO HACER EL BIA</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1. Listá los procesos del negocio (tomalos del mapa de procesos si lo tenés).</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2. Con el responsable de cada proceso, evaluá el impacto de una interrupción en 4 dimensiones (1-5).</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>3. Definí RTO (cuánto tarda en volver a funcionar), RPO (cuántos datos podés perder) y MTPD (límite máximo tolerable).</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>4. Anotá las dependencias: sistemas, personas clave, proveedores, infraestructura.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5. Los procesos Críticos son la prioridad del plan de continuidad.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>TIP: en SGI360 el BIA alimenta los planes de continuidad y el mapa de procesos → logismart.ar</v>
+    <row r="1" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>